--- a/WorkBot/main/data/orders/US Foods/US Foods_Bakery_20260826.xlsx
+++ b/WorkBot/main/data/orders/US Foods/US Foods_Bakery_20260826.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,6 +605,426 @@
         <v>26.99</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6435380</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hals - Lime</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5607194</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hals - Lemon</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4688660</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hals - Black Cherry</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8457368</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oil - Corn</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>9176843</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cereal - Rice Crispy</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>22.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7863400</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nutella</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="E17" t="n">
+        <v>47.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3791747</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Can - Roasted Red Pepper (Strips)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3737152</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Honey - Jug</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2825368</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sausage - Chicken Patty</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>9192185</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tuna - Ahi (Sesame Seared)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="E21" t="n">
+        <v>90.61</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7196012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagel - Plain GF</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>74.13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9047468</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Egg Patty</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>442.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2096568</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Peanut Butter - Creamy</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55.37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1089599</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Half &amp; Half</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="E25" t="n">
+        <v>76.89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1659526</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Oat Milk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="E26" t="n">
+        <v>60.32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6432884</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pepper Jack (Sliced)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E27" t="n">
+        <v>104.97</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1027629</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cheddar - (Sliced)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="E28" t="n">
+        <v>257.16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2739175</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sour Cream</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="E29" t="n">
+        <v>25.84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5353834</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Donut - Sour Cream (3oz)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E30" t="n">
+        <v>227.96</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1268389</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Donut - Ring Raised</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E31" t="n">
+        <v>79.95999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
